--- a/business_report_forms/015_payroll_analytics_report_request_form--business_report_forms.xlsx
+++ b/business_report_forms/015_payroll_analytics_report_request_form--business_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'january'}</t>
+          <t>january</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'January'}</t>
+          <t>January</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'february'}</t>
+          <t>february</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'February'}</t>
+          <t>February</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'march'}</t>
+          <t>march</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'March'}</t>
+          <t>March</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'april'}</t>
+          <t>april</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'April'}</t>
+          <t>April</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'may'}</t>
+          <t>may</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'May'}</t>
+          <t>May</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'june'}</t>
+          <t>june</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'June'}</t>
+          <t>June</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'july'}</t>
+          <t>july</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'July'}</t>
+          <t>July</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'august'}</t>
+          <t>august</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'August'}</t>
+          <t>August</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'september'}</t>
+          <t>september</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'September'}</t>
+          <t>September</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'october'}</t>
+          <t>october</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'October'}</t>
+          <t>October</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'november'}</t>
+          <t>november</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'November'}</t>
+          <t>November</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'december'}</t>
+          <t>december</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'December'}</t>
+          <t>December</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'yearly'}</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Yearly'}</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'yearly'}</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Yearly'}</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'employee_1'}</t>
+          <t>employee_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Employee 1'}</t>
+          <t>Employee 1</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'employee_2'}</t>
+          <t>employee_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Employee 2'}</t>
+          <t>Employee 2</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'employee_3'}</t>
+          <t>employee_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Employee 3'}</t>
+          <t>Employee 3</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'A'}</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'B'}</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
